--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-08-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>£42.21</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulation-online.com/product/celotex-xr4150-150mm/</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a9d16b55+79621]
-	GetHandleVerifier [0x0x7ff6a9d16bb0+79712]
-	(No symbol) [0x0x7ff6a9aac0ea]
-	(No symbol) [0x0x7ff6a9b02f56]
-	(No symbol) [0x0x7ff6a9b0320c]
-	(No symbol) [0x0x7ff6a9b565b7]
-	(No symbol) [0x0x7ff6a9b2b17f]
-	(No symbol) [0x0x7ff6a9b533d0]
-	(No symbol) [0x0x7ff6a9b2af13]
-	(No symbol) [0x0x7ff6a9af4151]
-	(No symbol) [0x0x7ff6a9af4ee3]
-	GetHandleVerifier [0x0x7ff6a9fd686d+2962461]
-	GetHandleVerifier [0x0x7ff6a9fd0b8d+2938685]
-	GetHandleVerifier [0x0x7ff6a9fef74d+3064573]
-	GetHandleVerifier [0x0x7ff6a9d30c9e+186446]
-	GetHandleVerifier [0x0x7ff6a9d38a6f+218655]
-	GetHandleVerifier [0x0x7ff6a9d1f944+115956]
-	GetHandleVerifier [0x0x7ff6a9d1faf9+116393]
-	GetHandleVerifier [0x0x7ff6a9d05f28+10968]
+	GetHandleVerifier [0x0x7ff6abac6b55+79621]
+	GetHandleVerifier [0x0x7ff6abac6bb0+79712]
+	(No symbol) [0x0x7ff6ab85c0ea]
+	(No symbol) [0x0x7ff6ab8b2f56]
+	(No symbol) [0x0x7ff6ab8b320c]
+	(No symbol) [0x0x7ff6ab9065b7]
+	(No symbol) [0x0x7ff6ab8db17f]
+	(No symbol) [0x0x7ff6ab9033d0]
+	(No symbol) [0x0x7ff6ab8daf13]
+	(No symbol) [0x0x7ff6ab8a4151]
+	(No symbol) [0x0x7ff6ab8a4ee3]
+	GetHandleVerifier [0x0x7ff6abd8686d+2962461]
+	GetHandleVerifier [0x0x7ff6abd80b8d+2938685]
+	GetHandleVerifier [0x0x7ff6abd9f74d+3064573]
+	GetHandleVerifier [0x0x7ff6abae0c9e+186446]
+	GetHandleVerifier [0x0x7ff6abae8a6f+218655]
+	GetHandleVerifier [0x0x7ff6abacf944+115956]
+	GetHandleVerifier [0x0x7ff6abacfaf9+116393]
+	GetHandleVerifier [0x0x7ff6abab5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
